--- a/Job_Outreach_Tracker.xlsx
+++ b/Job_Outreach_Tracker.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +40,12 @@
       <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -4507,6 +4513,26 @@
           <t>Razorpay</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:08</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -4532,6 +4558,26 @@
           <t>Razorpay</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:09</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4557,6 +4603,26 @@
           <t>HCLTech</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:10</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -4582,6 +4648,26 @@
           <t>Swiggy</t>
         </is>
       </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:11</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4607,6 +4693,26 @@
           <t>Flipkart</t>
         </is>
       </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:12</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4632,6 +4738,26 @@
           <t>IBM India</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:13</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4657,6 +4783,26 @@
           <t>Accenture India</t>
         </is>
       </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:14</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4682,6 +4828,26 @@
           <t>Wipro</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:15</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>2026-06-31</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4707,6 +4873,26 @@
           <t>IBM India</t>
         </is>
       </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:16</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>2026-06-32</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4732,6 +4918,26 @@
           <t>Cognizant</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:17</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>2026-06-33</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4757,6 +4963,26 @@
           <t>Genpact</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:18</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>2026-06-34</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -4782,6 +5008,26 @@
           <t>TCS</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:19</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>2026-06-35</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -4807,6 +5053,26 @@
           <t>Wipro</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:20</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>2026-06-36</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -4832,6 +5098,26 @@
           <t>Genpact</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:21</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>2026-06-37</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -4857,6 +5143,26 @@
           <t>Swiggy</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:22</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>2026-06-38</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -4882,6 +5188,26 @@
           <t>TCS</t>
         </is>
       </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:23</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>2026-06-39</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -4907,6 +5233,26 @@
           <t>TCS</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:24</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>2026-06-40</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -4932,6 +5278,26 @@
           <t>Infosys</t>
         </is>
       </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:25</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>2026-06-41</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -4957,6 +5323,26 @@
           <t>IBM India</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:26</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>2026-06-42</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -4982,6 +5368,26 @@
           <t>Razorpay</t>
         </is>
       </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:27</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>2026-06-43</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -5007,6 +5413,26 @@
           <t>Flipkart</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:28</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>2026-06-44</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -5032,6 +5458,26 @@
           <t>LTIMindtree</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:29</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>2026-06-45</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -5057,6 +5503,26 @@
           <t>TCS</t>
         </is>
       </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:30</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>2026-06-46</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -5082,6 +5548,26 @@
           <t>Swiggy</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:31</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>2026-06-47</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -5107,6 +5593,26 @@
           <t>Genpact</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:32</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>2026-06-48</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -5132,6 +5638,26 @@
           <t>IBM India</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:33</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>2026-06-49</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -5157,6 +5683,26 @@
           <t>IBM India</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:34</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>2026-06-50</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -5182,6 +5728,26 @@
           <t>Capgemini India</t>
         </is>
       </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:35</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>2026-06-51</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -5207,6 +5773,26 @@
           <t>IBM India</t>
         </is>
       </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:36</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>2026-06-52</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -5232,6 +5818,26 @@
           <t>Cognizant</t>
         </is>
       </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:37</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>2026-06-53</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -5257,6 +5863,26 @@
           <t>Ola Cabs</t>
         </is>
       </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:38</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>2026-06-54</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -5282,6 +5908,26 @@
           <t>Capgemini India</t>
         </is>
       </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:39</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>2026-06-55</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -5307,6 +5953,26 @@
           <t>Wipro</t>
         </is>
       </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:40</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>2026-06-56</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -5332,6 +5998,26 @@
           <t>IBM India</t>
         </is>
       </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:41</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>2026-06-57</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -5357,6 +6043,26 @@
           <t>Zomato</t>
         </is>
       </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:42</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>2026-06-58</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -5382,6 +6088,26 @@
           <t>Tech Mahindra</t>
         </is>
       </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:43</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>2026-06-59</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -5407,6 +6133,26 @@
           <t>Capgemini India</t>
         </is>
       </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:44</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>2026-06-60</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -5432,6 +6178,26 @@
           <t>Genpact</t>
         </is>
       </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:45</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>2026-06-61</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -5457,6 +6223,26 @@
           <t>Ola Cabs</t>
         </is>
       </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:46</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>2026-06-62</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -5482,6 +6268,26 @@
           <t>Swiggy</t>
         </is>
       </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:47</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>2026-06-63</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -5507,6 +6313,26 @@
           <t>HCLTech</t>
         </is>
       </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:48</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>2026-06-64</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -5532,6 +6358,26 @@
           <t>Wipro</t>
         </is>
       </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:49</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>2026-06-65</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -5557,6 +6403,26 @@
           <t>Accenture India</t>
         </is>
       </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:50</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>2026-06-66</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -5582,6 +6448,26 @@
           <t>Genpact</t>
         </is>
       </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:51</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>2026-06-67</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -5607,6 +6493,26 @@
           <t>Tech Mahindra</t>
         </is>
       </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:52</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>2026-06-68</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -5632,6 +6538,26 @@
           <t>Infosys</t>
         </is>
       </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:53</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>2026-06-69</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -5657,6 +6583,26 @@
           <t>LTIMindtree</t>
         </is>
       </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:54</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>2026-06-70</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -5682,6 +6628,26 @@
           <t>Ola Cabs</t>
         </is>
       </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:55</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>2026-06-71</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -5707,6 +6673,26 @@
           <t>Flipkart</t>
         </is>
       </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:56</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>2026-06-72</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -5732,6 +6718,26 @@
           <t>Zomato</t>
         </is>
       </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>2026-06-19 03:57</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Quick question regarding TCS's AI team</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>2026-06-73</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -5757,6 +6763,26 @@
           <t>PhonePe</t>
         </is>
       </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:20</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Quick question regarding PhonePe's AI team</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -5782,6 +6808,26 @@
           <t>Paytm</t>
         </is>
       </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:20</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Quick question regarding Paytm's AI team</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -5807,6 +6853,26 @@
           <t>Paytm</t>
         </is>
       </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:21</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Quick question regarding Paytm's AI team</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -5832,6 +6898,26 @@
           <t>PhonePe</t>
         </is>
       </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:22</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Quick question regarding PhonePe's AI team</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -5857,6 +6943,26 @@
           <t>Capgemini India</t>
         </is>
       </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:22</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Quick question regarding Capgemini India's AI team</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -5882,6 +6988,26 @@
           <t>Ola Cabs</t>
         </is>
       </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:23</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Quick question regarding Ola Cabs's AI team</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -5907,6 +7033,26 @@
           <t>HCLTech</t>
         </is>
       </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:23</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Quick question regarding HCLTech's AI team</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -5932,6 +7078,26 @@
           <t>Genpact</t>
         </is>
       </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:24</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Quick question regarding Genpact's AI team</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -5957,6 +7123,26 @@
           <t>Flipkart</t>
         </is>
       </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:25</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Quick question regarding Flipkart's AI team</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -5982,6 +7168,26 @@
           <t>Tech Mahindra</t>
         </is>
       </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:25</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Quick question regarding Tech Mahindra's AI team</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -6007,6 +7213,26 @@
           <t>Capgemini India</t>
         </is>
       </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:26</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Quick question regarding Capgemini India's AI team</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -6032,6 +7258,26 @@
           <t>Accenture India</t>
         </is>
       </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:26</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Quick question regarding Accenture India's AI team</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -6057,6 +7303,26 @@
           <t>Tech Mahindra</t>
         </is>
       </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:27</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Quick question regarding Tech Mahindra's AI team</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -6082,6 +7348,26 @@
           <t>IBM India</t>
         </is>
       </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:28</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Quick question regarding IBM India's AI team</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -6107,6 +7393,26 @@
           <t>Cognizant</t>
         </is>
       </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:28</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Quick question regarding Cognizant's AI team</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -6132,6 +7438,26 @@
           <t>Capgemini India</t>
         </is>
       </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:29</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Quick question regarding Capgemini India's AI team</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -6157,6 +7483,26 @@
           <t>Wipro</t>
         </is>
       </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:29</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Quick question regarding Wipro's AI team</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -6182,6 +7528,26 @@
           <t>Zomato</t>
         </is>
       </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:30</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Quick question regarding Zomato's AI team</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -6207,6 +7573,26 @@
           <t>Cognizant</t>
         </is>
       </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:30</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Quick question regarding Cognizant's AI team</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -6232,6 +7618,26 @@
           <t>Flipkart</t>
         </is>
       </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:31</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Quick question regarding Flipkart's AI team</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -6257,6 +7663,26 @@
           <t>Tech Mahindra</t>
         </is>
       </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:32</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Quick question regarding Tech Mahindra's AI team</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -6282,6 +7708,26 @@
           <t>Wipro</t>
         </is>
       </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:32</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Quick question regarding Wipro's AI team</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -6307,6 +7753,26 @@
           <t>Tech Mahindra</t>
         </is>
       </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:33</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Quick question regarding Tech Mahindra's AI team</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -6332,6 +7798,26 @@
           <t>Infosys</t>
         </is>
       </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:33</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Quick question regarding Infosys's AI team</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -6357,6 +7843,26 @@
           <t>Razorpay</t>
         </is>
       </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>2026-06-20 14:34</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Quick question regarding Razorpay's AI team</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -6382,6 +7888,11 @@
           <t>TCS</t>
         </is>
       </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -6407,6 +7918,11 @@
           <t>LTIMindtree</t>
         </is>
       </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -6432,6 +7948,11 @@
           <t>TCS</t>
         </is>
       </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -6457,6 +7978,11 @@
           <t>HCLTech</t>
         </is>
       </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -6482,6 +8008,11 @@
           <t>IBM India</t>
         </is>
       </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -6507,6 +8038,11 @@
           <t>TCS</t>
         </is>
       </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -6532,6 +8068,11 @@
           <t>Infosys</t>
         </is>
       </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -6557,6 +8098,11 @@
           <t>Genpact</t>
         </is>
       </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -6582,6 +8128,11 @@
           <t>Ola Cabs</t>
         </is>
       </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -6607,6 +8158,11 @@
           <t>Razorpay</t>
         </is>
       </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -6632,6 +8188,11 @@
           <t>HCLTech</t>
         </is>
       </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -6657,6 +8218,11 @@
           <t>Cognizant</t>
         </is>
       </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -6682,6 +8248,11 @@
           <t>Accenture India</t>
         </is>
       </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -6707,6 +8278,11 @@
           <t>Ola Cabs</t>
         </is>
       </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -6732,6 +8308,11 @@
           <t>LTIMindtree</t>
         </is>
       </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -6757,6 +8338,11 @@
           <t>TCS</t>
         </is>
       </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -6782,6 +8368,11 @@
           <t>Flipkart</t>
         </is>
       </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -6807,6 +8398,11 @@
           <t>Capgemini India</t>
         </is>
       </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -6832,6 +8428,11 @@
           <t>Swiggy</t>
         </is>
       </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -6857,6 +8458,11 @@
           <t>Accenture India</t>
         </is>
       </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -6882,6 +8488,11 @@
           <t>Flipkart</t>
         </is>
       </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -6907,6 +8518,11 @@
           <t>LTIMindtree</t>
         </is>
       </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -6932,6 +8548,11 @@
           <t>Genpact</t>
         </is>
       </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -6957,6 +8578,11 @@
           <t>Paytm</t>
         </is>
       </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -6982,6 +8608,11 @@
           <t>Ola Cabs</t>
         </is>
       </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -7007,6 +8638,11 @@
           <t>Genpact</t>
         </is>
       </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -7032,6 +8668,11 @@
           <t>Razorpay</t>
         </is>
       </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -7057,6 +8698,11 @@
           <t>Genpact</t>
         </is>
       </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -7082,6 +8728,11 @@
           <t>IBM India</t>
         </is>
       </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -7107,6 +8758,11 @@
           <t>Swiggy</t>
         </is>
       </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -7132,6 +8788,11 @@
           <t>Zomato</t>
         </is>
       </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -7157,6 +8818,11 @@
           <t>IBM India</t>
         </is>
       </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -7182,6 +8848,11 @@
           <t>PhonePe</t>
         </is>
       </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -7207,6 +8878,11 @@
           <t>Zomato</t>
         </is>
       </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -7232,6 +8908,11 @@
           <t>Genpact</t>
         </is>
       </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -7257,6 +8938,11 @@
           <t>LTIMindtree</t>
         </is>
       </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -7282,6 +8968,11 @@
           <t>Genpact</t>
         </is>
       </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -7307,6 +8998,11 @@
           <t>Capgemini India</t>
         </is>
       </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -7332,6 +9028,11 @@
           <t>Swiggy</t>
         </is>
       </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -7357,6 +9058,11 @@
           <t>PhonePe</t>
         </is>
       </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -7382,6 +9088,11 @@
           <t>Flipkart</t>
         </is>
       </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -7407,6 +9118,11 @@
           <t>Capgemini India</t>
         </is>
       </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -7432,6 +9148,11 @@
           <t>Wipro</t>
         </is>
       </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -7457,6 +9178,11 @@
           <t>Infosys</t>
         </is>
       </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -7482,6 +9208,11 @@
           <t>Ola Cabs</t>
         </is>
       </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -7507,6 +9238,11 @@
           <t>Accenture India</t>
         </is>
       </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -7532,6 +9268,11 @@
           <t>Infosys</t>
         </is>
       </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -7557,6 +9298,11 @@
           <t>TCS</t>
         </is>
       </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -7582,6 +9328,11 @@
           <t>Genpact</t>
         </is>
       </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -7607,6 +9358,11 @@
           <t>Zomato</t>
         </is>
       </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -7632,6 +9388,11 @@
           <t>HCLTech</t>
         </is>
       </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -7657,6 +9418,11 @@
           <t>Swiggy</t>
         </is>
       </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -7682,6 +9448,11 @@
           <t>Accenture India</t>
         </is>
       </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -7707,6 +9478,11 @@
           <t>HCLTech</t>
         </is>
       </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -7732,6 +9508,11 @@
           <t>Cognizant</t>
         </is>
       </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -7757,6 +9538,11 @@
           <t>Ola Cabs</t>
         </is>
       </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -7782,6 +9568,11 @@
           <t>Flipkart</t>
         </is>
       </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -7807,6 +9598,11 @@
           <t>Infosys</t>
         </is>
       </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -7832,6 +9628,11 @@
           <t>IBM India</t>
         </is>
       </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -7857,6 +9658,11 @@
           <t>Tech Mahindra</t>
         </is>
       </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -7882,6 +9688,11 @@
           <t>Ola Cabs</t>
         </is>
       </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -7907,6 +9718,11 @@
           <t>Zomato</t>
         </is>
       </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -7932,6 +9748,11 @@
           <t>Flipkart</t>
         </is>
       </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -7957,6 +9778,11 @@
           <t>Paytm</t>
         </is>
       </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -7982,6 +9808,11 @@
           <t>IBM India</t>
         </is>
       </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -8007,6 +9838,11 @@
           <t>Infosys</t>
         </is>
       </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -8032,6 +9868,11 @@
           <t>Swiggy</t>
         </is>
       </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -8057,6 +9898,11 @@
           <t>LTIMindtree</t>
         </is>
       </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -8082,6 +9928,11 @@
           <t>Infosys</t>
         </is>
       </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -8107,6 +9958,11 @@
           <t>Capgemini India</t>
         </is>
       </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -8132,6 +9988,11 @@
           <t>Swiggy</t>
         </is>
       </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -8157,6 +10018,11 @@
           <t>Swiggy</t>
         </is>
       </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -8182,6 +10048,11 @@
           <t>Swiggy</t>
         </is>
       </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -8207,6 +10078,11 @@
           <t>PhonePe</t>
         </is>
       </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -8232,6 +10108,11 @@
           <t>Zomato</t>
         </is>
       </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -8257,6 +10138,11 @@
           <t>TCS</t>
         </is>
       </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -8282,6 +10168,11 @@
           <t>HCLTech</t>
         </is>
       </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -8307,6 +10198,11 @@
           <t>LTIMindtree</t>
         </is>
       </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -8332,6 +10228,11 @@
           <t>Ola Cabs</t>
         </is>
       </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -8357,6 +10258,11 @@
           <t>Genpact</t>
         </is>
       </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -8382,6 +10288,11 @@
           <t>Cognizant</t>
         </is>
       </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -8407,6 +10318,11 @@
           <t>Wipro</t>
         </is>
       </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -8432,6 +10348,11 @@
           <t>Flipkart</t>
         </is>
       </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -8457,6 +10378,11 @@
           <t>Infosys</t>
         </is>
       </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -8482,6 +10408,11 @@
           <t>Genpact</t>
         </is>
       </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -8507,6 +10438,11 @@
           <t>Wipro</t>
         </is>
       </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -8532,6 +10468,11 @@
           <t>Wipro</t>
         </is>
       </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -8557,6 +10498,11 @@
           <t>Cognizant</t>
         </is>
       </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -8582,6 +10528,11 @@
           <t>LTIMindtree</t>
         </is>
       </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -8607,6 +10558,11 @@
           <t>TCS</t>
         </is>
       </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -8632,6 +10588,11 @@
           <t>Tech Mahindra</t>
         </is>
       </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -8657,6 +10618,11 @@
           <t>LTIMindtree</t>
         </is>
       </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -8682,6 +10648,11 @@
           <t>Accenture India</t>
         </is>
       </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -8707,6 +10678,11 @@
           <t>Paytm</t>
         </is>
       </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -8732,6 +10708,11 @@
           <t>Infosys</t>
         </is>
       </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -8757,6 +10738,11 @@
           <t>Ola Cabs</t>
         </is>
       </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -8782,6 +10768,11 @@
           <t>Paytm</t>
         </is>
       </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -8807,6 +10798,11 @@
           <t>HCLTech</t>
         </is>
       </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -8832,6 +10828,11 @@
           <t>Ola Cabs</t>
         </is>
       </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -8857,6 +10858,11 @@
           <t>Infosys</t>
         </is>
       </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -8882,6 +10888,11 @@
           <t>Infosys</t>
         </is>
       </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -8907,6 +10918,11 @@
           <t>Wipro</t>
         </is>
       </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -8932,6 +10948,11 @@
           <t>Infosys</t>
         </is>
       </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -8957,6 +10978,11 @@
           <t>Ola Cabs</t>
         </is>
       </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -8982,6 +11008,11 @@
           <t>Accenture India</t>
         </is>
       </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -9007,6 +11038,11 @@
           <t>Paytm</t>
         </is>
       </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -9032,6 +11068,11 @@
           <t>Wipro</t>
         </is>
       </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -9057,6 +11098,11 @@
           <t>Flipkart</t>
         </is>
       </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -9082,6 +11128,11 @@
           <t>LTIMindtree</t>
         </is>
       </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -9107,6 +11158,11 @@
           <t>Wipro</t>
         </is>
       </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -9132,6 +11188,11 @@
           <t>Accenture India</t>
         </is>
       </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -9157,6 +11218,11 @@
           <t>IBM India</t>
         </is>
       </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -9182,6 +11248,11 @@
           <t>IBM India</t>
         </is>
       </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -9207,6 +11278,11 @@
           <t>Wipro</t>
         </is>
       </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -9232,6 +11308,11 @@
           <t>Paytm</t>
         </is>
       </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -9257,6 +11338,11 @@
           <t>Capgemini India</t>
         </is>
       </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -9282,6 +11368,11 @@
           <t>TCS</t>
         </is>
       </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -9307,6 +11398,11 @@
           <t>Cognizant</t>
         </is>
       </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -9332,6 +11428,11 @@
           <t>Ola Cabs</t>
         </is>
       </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -9357,6 +11458,11 @@
           <t>Swiggy</t>
         </is>
       </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -9382,6 +11488,11 @@
           <t>Razorpay</t>
         </is>
       </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -9407,6 +11518,11 @@
           <t>Wipro</t>
         </is>
       </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -9432,6 +11548,11 @@
           <t>Infosys</t>
         </is>
       </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -9457,6 +11578,11 @@
           <t>Wipro</t>
         </is>
       </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -9482,6 +11608,11 @@
           <t>IBM India</t>
         </is>
       </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -9507,6 +11638,11 @@
           <t>Paytm</t>
         </is>
       </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -9532,6 +11668,11 @@
           <t>Tech Mahindra</t>
         </is>
       </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -9557,6 +11698,11 @@
           <t>Swiggy</t>
         </is>
       </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -9582,6 +11728,11 @@
           <t>Zomato</t>
         </is>
       </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -9607,6 +11758,11 @@
           <t>Cognizant</t>
         </is>
       </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -9632,6 +11788,11 @@
           <t>Capgemini India</t>
         </is>
       </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -9657,6 +11818,11 @@
           <t>HCLTech</t>
         </is>
       </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -9682,6 +11848,11 @@
           <t>Swiggy</t>
         </is>
       </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -9707,6 +11878,11 @@
           <t>PhonePe</t>
         </is>
       </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -9732,6 +11908,11 @@
           <t>TCS</t>
         </is>
       </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -9757,6 +11938,11 @@
           <t>Swiggy</t>
         </is>
       </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -9782,6 +11968,11 @@
           <t>Cognizant</t>
         </is>
       </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -9807,6 +11998,11 @@
           <t>Paytm</t>
         </is>
       </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -9832,6 +12028,11 @@
           <t>Genpact</t>
         </is>
       </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -9857,6 +12058,11 @@
           <t>Flipkart</t>
         </is>
       </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -9882,6 +12088,11 @@
           <t>Cognizant</t>
         </is>
       </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -9907,6 +12118,11 @@
           <t>Zomato</t>
         </is>
       </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -9932,6 +12148,11 @@
           <t>HCLTech</t>
         </is>
       </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -9957,6 +12178,11 @@
           <t>TCS</t>
         </is>
       </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -9982,6 +12208,11 @@
           <t>Paytm</t>
         </is>
       </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -10007,6 +12238,11 @@
           <t>Swiggy</t>
         </is>
       </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -10032,6 +12268,11 @@
           <t>Swiggy</t>
         </is>
       </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -10057,6 +12298,11 @@
           <t>Ola Cabs</t>
         </is>
       </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -10082,6 +12328,11 @@
           <t>Paytm</t>
         </is>
       </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -10107,6 +12358,11 @@
           <t>Flipkart</t>
         </is>
       </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -10132,6 +12388,11 @@
           <t>IBM India</t>
         </is>
       </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -10157,6 +12418,11 @@
           <t>TCS</t>
         </is>
       </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -10182,6 +12448,11 @@
           <t>Tech Mahindra</t>
         </is>
       </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -10207,6 +12478,11 @@
           <t>Infosys</t>
         </is>
       </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -10232,6 +12508,11 @@
           <t>Ola Cabs</t>
         </is>
       </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -10257,6 +12538,11 @@
           <t>Razorpay</t>
         </is>
       </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -10282,6 +12568,11 @@
           <t>Accenture India</t>
         </is>
       </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -10307,6 +12598,11 @@
           <t>IBM India</t>
         </is>
       </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -10332,6 +12628,11 @@
           <t>Razorpay</t>
         </is>
       </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -10357,6 +12658,11 @@
           <t>Accenture India</t>
         </is>
       </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -10382,6 +12688,11 @@
           <t>Ola Cabs</t>
         </is>
       </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -10407,6 +12718,11 @@
           <t>LTIMindtree</t>
         </is>
       </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -10432,6 +12748,11 @@
           <t>TCS</t>
         </is>
       </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -10457,6 +12778,11 @@
           <t>Ola Cabs</t>
         </is>
       </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -10482,6 +12808,11 @@
           <t>Paytm</t>
         </is>
       </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -10507,6 +12838,11 @@
           <t>PhonePe</t>
         </is>
       </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -10530,6 +12866,11 @@
       <c r="E331" t="inlineStr">
         <is>
           <t>HCLTech</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Failed to Send</t>
         </is>
       </c>
     </row>
